--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -975,7 +975,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.6.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y93"/>
+  <dimension ref="A1:Y81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: a real race-horse，Pretty little Bar-</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 152â€¢TE</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L30: isolated marker/symbol line :: e</t>
@@ -634,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -650,7 +654,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L189: line starts with digit/letter garbage token | suspicious token(s): 1The (letter/digit mix) :: 1The free-for-all pace, which rumor</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •RIGHT•</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>625</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -688,7 +692,7 @@
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>L664: candidate OCR token mismatch vs other OCR: "appealed" vs "appeal" :: O'Loughlin, and Sheridan was appealed-</t>
+          <t>L132: candidate OCR token mismatch vs other OCR: "trct" vs "tret" :: win the 2.25 trct, as he can beat 2.13</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr"/>
@@ -704,12 +708,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L141: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Kalamazoo, Mich.,Aug.â€” Feature-</t>
+          <t>L24: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: thrd and fourth ， between ll. O. Me-</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: Buyin â‚¬</t>
+          <t>L62: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 152•TE</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -737,7 +741,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L471: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: ******* â€¢â€¢â€¢â€¢</t>
+          <t>L189: line starts with digit/letter garbage token | suspicious token(s): 1The (letter/digit mix) :: 1The free-for-all pace, which rumor</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -769,7 +773,11 @@
       </c>
       <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr"/>
-      <c r="F4" s="1" t="inlineStr"/>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>L664: candidate OCR token mismatch vs other OCR: "appealed" vs "appeal" :: O'Loughlin, and Sheridan was appealed-</t>
+        </is>
+      </c>
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr">
         <is>
@@ -783,12 +791,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L159: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Time â€” 2.08 Â½, 2.09 Â½.</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢RIGHTâ€¢</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Buyin €</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -810,13 +818,13 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John. ... 32</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John. ... 32</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L478: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----------0 F -</t>
+          <t>L362: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •1</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -834,12 +842,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>127</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -858,12 +866,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L185: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â€¦... 22 4</t>
+          <t>L175: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: Time-2.06 ½ 2 ， 2.05, 2.07</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L108: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Chicago, Aug. 4â€”The pace set By</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •RIGHT•</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -885,13 +893,13 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L439: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John ...618</t>
+          <t>L439: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John ...618</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L916: line starts with punctuation glued to text :: **THE HOUSE. OF GOOD CLOTHES"</t>
+          <t>L366: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton 27</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -933,12 +941,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L340: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Philadelphia, Aug. 4 â€” Accused of</t>
+          <t>L180: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：：.</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L173: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Me for Hankâ€™s Pne Tree Circuit</t>
+          <t>L220: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -955,16 +963,20 @@
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
-          <t>L185: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â€¦... 22 4</t>
+          <t>L185: symbol-only separator/garbage line | punctuation artifact: repeated periods :: …... 22 4</t>
         </is>
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. Croix .. .586</t>
+          <t>L441: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. Croix .. .586</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L440: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton . .586</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -1004,12 +1016,12 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L404: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�£</t>
+          <t>L404: stray/suspicious non-ASCII glyph(s): U+53E3 CJK UNIFIED IDEOGRAPH-53E3 | isolated marker/symbol line :: 口</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: -last week. Stafford, Fred Jamiesonâ€™s</t>
+          <t>L308: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ League Standing</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1031,11 +1043,15 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L446: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Wilkes (Cox .. ).............111 â€”</t>
+          <t>L446: punctuation artifact: repeated periods :: Wilkes (Cox .. ).............111 —</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr"/>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>L478: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----------0 F -</t>
+        </is>
+      </c>
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr"/>
       <c r="V7" s="1" t="inlineStr"/>
@@ -1051,7 +1067,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -1075,12 +1091,12 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L428: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Washingtonâ€”â€”</t>
+          <t>L405: stray/suspicious non-ASCII glyph(s): U+25A1 WHITE SQUARE | isolated marker/symbol line :: □</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L334: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1106,7 +1122,11 @@
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
-      <c r="S8" s="1" t="inlineStr"/>
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>L916: line starts with punctuation glued to text :: **THE HOUSE. OF GOOD CLOTHES"</t>
+        </is>
+      </c>
       <c r="T8" s="1" t="inlineStr"/>
       <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr"/>
@@ -1144,14 +1164,10 @@
           <t>L227: suspicious token(s): 17c (letter/digit mix) :: LISLE SOX, only 17c. a pair. Younever</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L431: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Russell, Cicotte and</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L269: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Kalamazoo, Mich., -Aug.â€” Feature-</t>
+          <t>L335: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Pct. •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1193,12 +1209,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1211,14 +1227,10 @@
           <t>L228: suspicious token(s): 25c (letter/digit mix) :: buy these less than 25c.</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L434: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Philadelphiaâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L308: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ League Standing</t>
+          <t>L336: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .604•</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1265,7 +1277,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1275,17 +1287,13 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L808: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 02000030x (letter/digit mix) :: . .02000030xâ€”7 11 1</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L438: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Falkenberk,</t>
-        </is>
-      </c>
+          <t>L808: suspicious token(s): 02000030x (letter/digit mix) :: . .02000030x—7 11 1</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Philadelphia, Aug. 4â€”Accused of</t>
+          <t>L337: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1327,12 +1335,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1342,17 +1350,13 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>L820: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150xâ€”6 14 1</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L443: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At New York â€”</t>
-        </is>
-      </c>
+          <t>L820: punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150x—6 14 1</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L338: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
@@ -1409,17 +1413,13 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223xâ€”13 19 1</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L450: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Chicago â€”</t>
-        </is>
-      </c>
+          <t>L872: punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223x—13 19 1</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L335: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Pct. â€¢</t>
+          <t>L339: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .265 •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1475,14 +1475,10 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L456: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Pittsburghâ€”-</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L336: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .604â€¢</t>
+          <t>L341: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
@@ -1504,7 +1500,7 @@
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Philadelphia. .. .000000402â€”6 10 3</t>
+          <t>L732: punctuation artifact: repeated periods :: Philadelphia. .. .000000402—6 10 3</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
@@ -1538,14 +1534,10 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L466: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Cincinnatiâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L337: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .563â€¢</t>
+          <t>L343: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
@@ -1557,7 +1549,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L220: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -1567,7 +1559,7 @@
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L734: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: St. Louis.........021000000â€”3 7 0</t>
+          <t>L734: punctuation artifact: repeated periods :: St. Louis.........021000000—3 7 0</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
@@ -1601,14 +1593,10 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At St. Louis â€”</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L338: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .563â€¢</t>
+          <t>L344: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
@@ -1630,7 +1618,7 @@
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L744: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Chicago .........300200000â€”5 4</t>
+          <t>L744: punctuation artifact: repeated periods :: Chicago .........300200000—5 4</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
@@ -1664,21 +1652,17 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L479: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: St. Louis... 021000000 â€” 3 70</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L339: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .265 â€¢</t>
+          <t>L345: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Lose •</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1715,14 +1699,10 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Doak, Harmon and Win-</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L346: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Two. •</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr"/>
@@ -1734,7 +1714,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L334: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
@@ -1766,14 +1746,10 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L495: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Coakley an</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L347: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .582•</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr"/>
@@ -1785,7 +1761,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L336: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .604•</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
@@ -1817,14 +1793,10 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L499: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Montrealâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>L344: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L348: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr"/>
@@ -1836,7 +1808,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L337: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -1846,7 +1818,7 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>L790: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Montreal ..........30300100201â€”7 10 3</t>
+          <t>L790: punctuation artifact: repeated periods :: Montreal ..........30300100201—7 10 3</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
@@ -1868,14 +1840,10 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L508: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Buffalo â€”</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>L345: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Lose â€¢</t>
+          <t>L349: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr"/>
@@ -1887,7 +1855,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L344: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L338: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .563•</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr">
@@ -1897,7 +1865,7 @@
       </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>L799: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Baltimore...........000111000â€”3 6 1</t>
+          <t>L799: punctuation artifact: repeated periods :: Baltimore...........000111000—3 6 1</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
@@ -1919,14 +1887,10 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L524: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Wilmington, Del., Aug. 4 â€” Buck "</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>L346: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Two. â€¢</t>
+          <t>L350: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | symbol-only separator/garbage line :: .255 ♦</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr"/>
@@ -1938,7 +1902,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L339: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .265 •</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -1948,7 +1912,7 @@
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L801: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Buffalo ............000000010â€”1 6 0</t>
+          <t>L801: punctuation artifact: repeated periods :: Buffalo ............000000010—1 6 0</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
@@ -1973,7 +1937,7 @@
       <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>L347: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .582â€¢</t>
+          <t>L352: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr"/>
@@ -1985,7 +1949,7 @@
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L356: isolated marker/symbol line :: 21</t>
+          <t>L341: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr">
@@ -1995,7 +1959,7 @@
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Detroit..........002000002â€”4 15 3</t>
+          <t>L818: punctuation artifact: repeated periods :: Detroit..........002000002—4 15 3</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
@@ -2020,7 +1984,7 @@
       <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>L348: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .540â€¢</t>
+          <t>L353: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • • • •</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr"/>
@@ -2032,7 +1996,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L357: isolated marker/symbol line :: 21</t>
+          <t>L343: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr">
@@ -2042,7 +2006,7 @@
       </c>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>L820: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150xâ€”6 14 1</t>
+          <t>L820: punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150x—6 14 1</t>
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr"/>
@@ -2067,7 +2031,7 @@
       <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>L349: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: .540â€¢</t>
+          <t>L362: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •1</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr"/>
@@ -2079,7 +2043,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L358: symbol-only separator/garbage line :: 27 21</t>
+          <t>L344: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -2114,7 +2078,7 @@
       <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>L350: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: .255 â™¦</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John. ... 32</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr"/>
@@ -2126,7 +2090,7 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L360: isolated marker/symbol line :: 36</t>
+          <t>L347: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .582•</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -2136,7 +2100,7 @@
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>L853: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Brooklyn .........102000310â€”7 12</t>
+          <t>L853: punctuation artifact: repeated periods :: Brooklyn .........102000310—7 12</t>
         </is>
       </c>
       <c r="R26" s="1" t="inlineStr"/>
@@ -2161,7 +2125,7 @@
       <c r="J27" s="1" t="inlineStr"/>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L366: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton 27</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr"/>
@@ -2173,7 +2137,7 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L410: isolated marker/symbol line :: Â°</t>
+          <t>L348: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
@@ -2183,7 +2147,7 @@
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L862: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: New York.........000001100â€”2 7 0</t>
+          <t>L862: punctuation artifact: repeated periods :: New York.........000001100—2 7 0</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2208,19 +2172,19 @@
       <c r="J28" s="1" t="inlineStr"/>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢ â€¢ â€¢</t>
+          <t>L406: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ St. Croix.</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L181: isolated marker/symbol line :: 111</t>
+          <t>L180: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：：.</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L411: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L349: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: .540•</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -2230,7 +2194,7 @@
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>L864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Pittsburg .......000000010â€”1 3 1</t>
+          <t>L864: punctuation artifact: repeated periods :: Pittsburg .......000000010—1 3 1</t>
         </is>
       </c>
       <c r="R28" s="1" t="inlineStr"/>
@@ -2255,29 +2219,29 @@
       <c r="J29" s="1" t="inlineStr"/>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>L362: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢1</t>
+          <t>L408: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ Bangor.........13</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L187: symbol-only separator/garbage line | punctuation artifact: repeated periods :: )... 642</t>
+          <t>L181: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L350: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | symbol-only separator/garbage line :: .255 ♦</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
-          <t>L479: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: St. Louis... 021000000 â€” 3 70</t>
+          <t>L479: punctuation artifact: repeated periods :: St. Louis... 021000000 — 3 70</t>
         </is>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223xâ€”13 19 1</t>
+          <t>L872: punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223x—13 19 1</t>
         </is>
       </c>
       <c r="R29" s="1" t="inlineStr"/>
@@ -2302,19 +2266,19 @@
       <c r="J30" s="1" t="inlineStr"/>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John. ... 32</t>
+          <t>L411: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L190: isolated marker/symbol line :: .</t>
+          <t>L185: symbol-only separator/garbage line | punctuation artifact: repeated periods :: …... 22 4</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L413: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L352: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr">
@@ -2324,7 +2288,7 @@
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Boston..........120000001â€” 4 7 1</t>
+          <t>L874: punctuation artifact: repeated periods :: Boston..........120000001— 4 7 1</t>
         </is>
       </c>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2349,19 +2313,19 @@
       <c r="J31" s="1" t="inlineStr"/>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>L366: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Fredericton 27</t>
+          <t>L412: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L191: isolated marker/symbol line :: :</t>
+          <t>L187: symbol-only separator/garbage line | punctuation artifact: repeated periods :: )... 642</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L414: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L353: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • • • •</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr">
@@ -2392,19 +2356,19 @@
       <c r="J32" s="1" t="inlineStr"/>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>L384: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Charlie Oâ€™Brien, the St. John club's</t>
+          <t>L413: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L192: symbol-only separator/garbage line :: . 3 3 3</t>
+          <t>L190: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L426: isolated marker/symbol line :: p</t>
+          <t>L356: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr">
@@ -2435,19 +2399,19 @@
       <c r="J33" s="1" t="inlineStr"/>
       <c r="K33" s="1" t="inlineStr">
         <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ St. Croix.</t>
+          <t>L414: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L230: isolated marker/symbol line :: 2</t>
+          <t>L191: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L427: isolated marker/symbol line :: I.</t>
+          <t>L357: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -2478,19 +2442,19 @@
       <c r="J34" s="1" t="inlineStr"/>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>L408: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ Bangor.........13</t>
+          <t>L439: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. John ...618</t>
         </is>
       </c>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L313: symbol-only separator/garbage line :: . 317.</t>
+          <t>L192: symbol-only separator/garbage line :: . 3 3 3</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L431: symbol-only separator/garbage line :: .600</t>
+          <t>L358: symbol-only separator/garbage line :: 27 21</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr">
@@ -2521,19 +2485,19 @@
       <c r="J35" s="1" t="inlineStr"/>
       <c r="K35" s="1" t="inlineStr">
         <is>
-          <t>L411: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L440: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Fredericton . .586</t>
         </is>
       </c>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L369: isolated marker/symbol line :: n</t>
+          <t>L230: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L432: symbol-only separator/garbage line :: .560</t>
+          <t>L360: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr">
@@ -2564,19 +2528,19 @@
       <c r="J36" s="1" t="inlineStr"/>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L441: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | punctuation artifact: repeated periods :: ♦ St. Croix .. .586</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L373: isolated marker/symbol line :: 21</t>
+          <t>L313: symbol-only separator/garbage line :: . 317.</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L433: symbol-only separator/garbage line :: .560</t>
+          <t>L362: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line | line starts with punctuation glued to text :: •1</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr">
@@ -2607,19 +2571,19 @@
       <c r="J37" s="1" t="inlineStr"/>
       <c r="K37" s="1" t="inlineStr">
         <is>
-          <t>L413: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L442: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ Bangor . . . .294</t>
         </is>
       </c>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L374: symbol-only separator/garbage line :: . 604</t>
+          <t>L369: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L434: symbol-only separator/garbage line :: .275</t>
+          <t>L410: isolated marker/symbol line :: °</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr">
@@ -2650,19 +2614,19 @@
       <c r="J38" s="1" t="inlineStr"/>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>L414: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â™¦</t>
+          <t>L471: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: ******* ••••</t>
         </is>
       </c>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L376: isolated marker/symbol line :: 21</t>
+          <t>L373: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L758: isolated marker/symbol line :: 1</t>
+          <t>L411: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2689,19 +2653,19 @@
       <c r="J39" s="1" t="inlineStr"/>
       <c r="K39" s="1" t="inlineStr">
         <is>
-          <t>L439: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. John ...618</t>
+          <t>L842: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L377: symbol-only separator/garbage line :: . 563</t>
+          <t>L374: symbol-only separator/garbage line :: . 604</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L759: isolated marker/symbol line :: 4</t>
+          <t>L412: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2726,21 +2690,17 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L440: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Fredericton . .586</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L379: isolated marker/symbol line :: 21</t>
+          <t>L376: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L840: isolated marker/symbol line :: %</t>
+          <t>L413: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2765,21 +2725,17 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â™¦ St. Croix .. .586</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L380: symbol-only separator/garbage line :: . 563</t>
+          <t>L377: symbol-only separator/garbage line :: . 563</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L842: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L414: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT | isolated marker/symbol line :: ♦</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2804,21 +2760,17 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: â™¦ Bangor . . . .294</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L382: isolated marker/symbol line :: 36</t>
+          <t>L379: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L844: symbol-only separator/garbage line | punctuation artifact: repeated exclamation marks :: 2/1/07!!!!!!!!!!!!!!</t>
+          <t>L426: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2843,21 +2795,17 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L446: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Wilkes (Cox .. ).............111 â€”</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L383: symbol-only separator/garbage line :: . 265</t>
+          <t>L380: symbol-only separator/garbage line :: . 563</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L846: symbol-only separator/garbage line :: 20 22</t>
+          <t>L427: isolated marker/symbol line :: I.</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2882,21 +2830,17 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L456: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Timeâ€”2.06%2, 2.05%, 2.07%.</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L384: isolated marker/symbol line :: 6</t>
+          <t>L382: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L881: isolated marker/symbol line :: a</t>
+          <t>L431: symbol-only separator/garbage line :: .600</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -2921,21 +2865,17 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L471: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: ******* â€¢â€¢â€¢â€¢</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L393: symbol-only separator/garbage line :: . 600</t>
+          <t>L383: symbol-only separator/garbage line :: . 265</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L886: isolated marker/symbol line :: :</t>
+          <t>L432: symbol-only separator/garbage line :: .560</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -2960,19 +2900,19 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”JUST A FEWâ€”</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L394: symbol-only separator/garbage line :: . 582</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr"/>
+          <t>L384: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>L433: symbol-only separator/garbage line :: .560</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr"/>
       <c r="R46" s="1" t="inlineStr"/>
@@ -2995,19 +2935,19 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L502: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Timeâ€”2.12, 2.08%, 1.07.</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L396: symbol-only separator/garbage line :: . 560</t>
-        </is>
-      </c>
-      <c r="O47" s="1" t="inlineStr"/>
+          <t>L393: symbol-only separator/garbage line :: . 600</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L434: symbol-only separator/garbage line :: .275</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr"/>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3030,19 +2970,19 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Wilmington, Del., Aug. 4â€”"Buck"</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L397: symbol-only separator/garbage line :: . 540</t>
-        </is>
-      </c>
-      <c r="O48" s="1" t="inlineStr"/>
+          <t>L394: symbol-only separator/garbage line :: . 582</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>L471: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: ******* ••••</t>
+        </is>
+      </c>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr"/>
       <c r="R48" s="1" t="inlineStr"/>
@@ -3065,19 +3005,19 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Next Game at Scullyâ€™s</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L399: symbol-only separator/garbage line :: . 560</t>
-        </is>
-      </c>
-      <c r="O49" s="1" t="inlineStr"/>
+          <t>L396: symbol-only separator/garbage line :: . 560</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>L758: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P49" s="1" t="inlineStr"/>
       <c r="Q49" s="1" t="inlineStr"/>
       <c r="R49" s="1" t="inlineStr"/>
@@ -3100,19 +3040,19 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L577: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: oneâ€� yesterday. Lajoie, while at bat,</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L400: symbol-only separator/garbage line :: . 540</t>
-        </is>
-      </c>
-      <c r="O50" s="1" t="inlineStr"/>
+          <t>L397: symbol-only separator/garbage line :: . 540</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>L759: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr"/>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3135,19 +3075,19 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L599: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Oâ€™Loughlin, and Sheridan was appeal-</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L402: symbol-only separator/garbage line :: . 275</t>
-        </is>
-      </c>
-      <c r="O51" s="1" t="inlineStr"/>
+          <t>L399: symbol-only separator/garbage line :: . 560</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr">
+        <is>
+          <t>L806: symbol-only separator/garbage line :: .010000000—1 2 2</t>
+        </is>
+      </c>
       <c r="P51" s="1" t="inlineStr"/>
       <c r="Q51" s="1" t="inlineStr"/>
       <c r="R51" s="1" t="inlineStr"/>
@@ -3170,19 +3110,19 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L710: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Morey or PetÃ¨ Condon the other,</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L403: symbol-only separator/garbage line :: . 255</t>
-        </is>
-      </c>
-      <c r="O52" s="1" t="inlineStr"/>
+          <t>L400: symbol-only separator/garbage line :: . 540</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>L840: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P52" s="1" t="inlineStr"/>
       <c r="Q52" s="1" t="inlineStr"/>
       <c r="R52" s="1" t="inlineStr"/>
@@ -3205,19 +3145,19 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: at St. John to-morrow.â€”J. D. B.</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L404: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�£</t>
-        </is>
-      </c>
-      <c r="O53" s="1" t="inlineStr"/>
+          <t>L402: symbol-only separator/garbage line :: . 275</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>L842: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P53" s="1" t="inlineStr"/>
       <c r="Q53" s="1" t="inlineStr"/>
       <c r="R53" s="1" t="inlineStr"/>
@@ -3240,19 +3180,19 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L730: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At St Louisâ€”</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L405: isolated marker/symbol line :: â–¡</t>
-        </is>
-      </c>
-      <c r="O54" s="1" t="inlineStr"/>
+          <t>L403: symbol-only separator/garbage line :: . 255</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t>L844: symbol-only separator/garbage line | punctuation artifact: repeated exclamation marks :: 2/1/07!!!!!!!!!!!!!!</t>
+        </is>
+      </c>
       <c r="P54" s="1" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr"/>
       <c r="R54" s="1" t="inlineStr"/>
@@ -3275,19 +3215,19 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Philadelphia. .. .000000402â€”6 10 3</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L436: isolated marker/symbol line :: 2</t>
-        </is>
-      </c>
-      <c r="O55" s="1" t="inlineStr"/>
+          <t>L404: stray/suspicious non-ASCII glyph(s): U+53E3 CJK UNIFIED IDEOGRAPH-53E3 | isolated marker/symbol line :: 口</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>L846: symbol-only separator/garbage line :: 20 22</t>
+        </is>
+      </c>
       <c r="P55" s="1" t="inlineStr"/>
       <c r="Q55" s="1" t="inlineStr"/>
       <c r="R55" s="1" t="inlineStr"/>
@@ -3310,19 +3250,19 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L734: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: St. Louis.........021000000â€”3 7 0</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L445: isolated marker/symbol line :: 3</t>
-        </is>
-      </c>
-      <c r="O56" s="1" t="inlineStr"/>
+          <t>L405: stray/suspicious non-ASCII glyph(s): U+25A1 WHITE SQUARE | isolated marker/symbol line :: □</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>L881: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
       <c r="P56" s="1" t="inlineStr"/>
       <c r="Q56" s="1" t="inlineStr"/>
       <c r="R56" s="1" t="inlineStr"/>
@@ -3345,19 +3285,19 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L742: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Washingtonâ€”</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L452: isolated marker/symbol line :: 2</t>
-        </is>
-      </c>
-      <c r="O57" s="1" t="inlineStr"/>
+          <t>L436: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="inlineStr">
+        <is>
+          <t>L886: isolated marker/symbol line :: :</t>
+        </is>
+      </c>
       <c r="P57" s="1" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr"/>
       <c r="R57" s="1" t="inlineStr"/>
@@ -3380,16 +3320,12 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L744: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Chicago .........300200000â€”5 4</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L457: isolated marker/symbol line :: -</t>
+          <t>L445: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3415,16 +3351,12 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Washington. . . .020010000â€”3 10</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L459: isolated marker/symbol line :: 7</t>
+          <t>L452: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3450,16 +3382,12 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L748: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Russell. Cicotte and</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L460: isolated marker/symbol line :: 0</t>
+          <t>L457: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3485,16 +3413,12 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L768: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Torontoâ€”First game:</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L461: isolated marker/symbol line :: 1</t>
+          <t>L459: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -3520,16 +3444,12 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L770: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Jersey. . . .00001000000001â€”2 13 1</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L469: symbol-only separator/garbage line :: . 120000001-</t>
+          <t>L460: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3555,16 +3475,12 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L771: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Toronto. . . .00000001000000â€”1 12 4</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L470: isolated marker/symbol line :: 4</t>
+          <t>L461: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3590,16 +3506,12 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L786: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Montrealâ€”</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L471: isolated marker/symbol line :: 7</t>
+          <t>L469: symbol-only separator/garbage line :: . 120000001-</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3625,16 +3537,12 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L788: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Providence. . . .10200120000â€”6 13 3</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L472: isolated marker/symbol line :: 1</t>
+          <t>L470: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3660,16 +3568,12 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L790: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Montreal ..........30300100201â€”7 10 3</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L485: isolated marker/symbol line :: 4</t>
+          <t>L471: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3695,16 +3599,12 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L792: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 2 Batteriesâ€”Sline, Reisigi and Ons-</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L491: isolated marker/symbol line :: 4</t>
+          <t>L472: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3730,16 +3630,12 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L797: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Buffaloâ€”</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L493: isolated marker/symbol line :: 8</t>
+          <t>L485: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3765,16 +3661,12 @@
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L799: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Baltimore...........000111000â€”3 6 1</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L494: isolated marker/symbol line :: 0</t>
+          <t>L491: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3800,16 +3692,12 @@
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L801: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Buffalo ............000000010â€”1 6 0</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L501: isolated marker/symbol line :: 3</t>
+          <t>L493: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3835,16 +3723,12 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L803: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Roth and Egan; Bebe,</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L502: isolated marker/symbol line :: 33</t>
+          <t>L494: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -3870,16 +3754,12 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L806: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: .010000000â€”1 2 2</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L504: isolated marker/symbol line :: 3</t>
+          <t>L501: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -3905,16 +3785,12 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L808: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 02000030x (letter/digit mix) :: . .02000030xâ€”7 11 1</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L510: isolated marker/symbol line :: 6</t>
+          <t>L502: isolated marker/symbol line :: 33</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -3940,16 +3816,12 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L810: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteries â€” Falkenberk, Kahler,</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L511: isolated marker/symbol line :: 1</t>
+          <t>L504: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -3975,16 +3847,12 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L816: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At New Yorkâ€”</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L513: isolated marker/symbol line :: 6</t>
+          <t>L510: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -4010,16 +3878,12 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Detroit..........002000002â€”4 15 3</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L514: isolated marker/symbol line :: 0</t>
+          <t>L511: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
@@ -4045,16 +3909,12 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L820: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 00000150x (letter/digit mix) :: New York.........00000150xâ€”6 14 1</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L605: isolated marker/symbol line :: 3</t>
+          <t>L513: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr"/>
@@ -4080,16 +3940,12 @@
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L822: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Willett, Dubue and Mc-</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L606: isolated marker/symbol line :: 0</t>
+          <t>L514: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr"/>
@@ -4115,16 +3971,12 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
       <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L842: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L740: isolated marker/symbol line :: R</t>
+          <t>L605: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr"/>
@@ -4150,14 +4002,14 @@
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
       <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L851: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Chicagoâ€”</t>
-        </is>
-      </c>
+      <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
-      <c r="N80" s="1" t="inlineStr"/>
+      <c r="N80" s="1" t="inlineStr">
+        <is>
+          <t>L606: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
       <c r="O80" s="1" t="inlineStr"/>
       <c r="P80" s="1" t="inlineStr"/>
       <c r="Q80" s="1" t="inlineStr"/>
@@ -4181,14 +4033,14 @@
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
       <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L853: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Brooklyn .........102000310â€”7 12</t>
-        </is>
-      </c>
+      <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
-      <c r="N81" s="1" t="inlineStr"/>
+      <c r="N81" s="1" t="inlineStr">
+        <is>
+          <t>L740: isolated marker/symbol line :: R</t>
+        </is>
+      </c>
       <c r="O81" s="1" t="inlineStr"/>
       <c r="P81" s="1" t="inlineStr"/>
       <c r="Q81" s="1" t="inlineStr"/>
@@ -4201,378 +4053,6 @@
       <c r="X81" s="1" t="inlineStr"/>
       <c r="Y81" s="1" t="inlineStr"/>
     </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr"/>
-      <c r="B82" s="1" t="inlineStr"/>
-      <c r="C82" s="1" t="inlineStr"/>
-      <c r="D82" s="1" t="inlineStr"/>
-      <c r="E82" s="1" t="inlineStr"/>
-      <c r="F82" s="1" t="inlineStr"/>
-      <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L855: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Chicago. . . . . .001000000â€”1 4</t>
-        </is>
-      </c>
-      <c r="L82" s="1" t="inlineStr"/>
-      <c r="M82" s="1" t="inlineStr"/>
-      <c r="N82" s="1" t="inlineStr"/>
-      <c r="O82" s="1" t="inlineStr"/>
-      <c r="P82" s="1" t="inlineStr"/>
-      <c r="Q82" s="1" t="inlineStr"/>
-      <c r="R82" s="1" t="inlineStr"/>
-      <c r="S82" s="1" t="inlineStr"/>
-      <c r="T82" s="1" t="inlineStr"/>
-      <c r="U82" s="1" t="inlineStr"/>
-      <c r="V82" s="1" t="inlineStr"/>
-      <c r="W82" s="1" t="inlineStr"/>
-      <c r="X82" s="1" t="inlineStr"/>
-      <c r="Y82" s="1" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr"/>
-      <c r="B83" s="1" t="inlineStr"/>
-      <c r="C83" s="1" t="inlineStr"/>
-      <c r="D83" s="1" t="inlineStr"/>
-      <c r="E83" s="1" t="inlineStr"/>
-      <c r="F83" s="1" t="inlineStr"/>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L857: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Allen and Miller; Moore,</t>
-        </is>
-      </c>
-      <c r="L83" s="1" t="inlineStr"/>
-      <c r="M83" s="1" t="inlineStr"/>
-      <c r="N83" s="1" t="inlineStr"/>
-      <c r="O83" s="1" t="inlineStr"/>
-      <c r="P83" s="1" t="inlineStr"/>
-      <c r="Q83" s="1" t="inlineStr"/>
-      <c r="R83" s="1" t="inlineStr"/>
-      <c r="S83" s="1" t="inlineStr"/>
-      <c r="T83" s="1" t="inlineStr"/>
-      <c r="U83" s="1" t="inlineStr"/>
-      <c r="V83" s="1" t="inlineStr"/>
-      <c r="W83" s="1" t="inlineStr"/>
-      <c r="X83" s="1" t="inlineStr"/>
-      <c r="Y83" s="1" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr"/>
-      <c r="B84" s="1" t="inlineStr"/>
-      <c r="C84" s="1" t="inlineStr"/>
-      <c r="D84" s="1" t="inlineStr"/>
-      <c r="E84" s="1" t="inlineStr"/>
-      <c r="F84" s="1" t="inlineStr"/>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
-      <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L860: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Pittsburgâ€”</t>
-        </is>
-      </c>
-      <c r="L84" s="1" t="inlineStr"/>
-      <c r="M84" s="1" t="inlineStr"/>
-      <c r="N84" s="1" t="inlineStr"/>
-      <c r="O84" s="1" t="inlineStr"/>
-      <c r="P84" s="1" t="inlineStr"/>
-      <c r="Q84" s="1" t="inlineStr"/>
-      <c r="R84" s="1" t="inlineStr"/>
-      <c r="S84" s="1" t="inlineStr"/>
-      <c r="T84" s="1" t="inlineStr"/>
-      <c r="U84" s="1" t="inlineStr"/>
-      <c r="V84" s="1" t="inlineStr"/>
-      <c r="W84" s="1" t="inlineStr"/>
-      <c r="X84" s="1" t="inlineStr"/>
-      <c r="Y84" s="1" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr"/>
-      <c r="B85" s="1" t="inlineStr"/>
-      <c r="C85" s="1" t="inlineStr"/>
-      <c r="D85" s="1" t="inlineStr"/>
-      <c r="E85" s="1" t="inlineStr"/>
-      <c r="F85" s="1" t="inlineStr"/>
-      <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L862: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: New York.........000001100â€”2 7 0</t>
-        </is>
-      </c>
-      <c r="L85" s="1" t="inlineStr"/>
-      <c r="M85" s="1" t="inlineStr"/>
-      <c r="N85" s="1" t="inlineStr"/>
-      <c r="O85" s="1" t="inlineStr"/>
-      <c r="P85" s="1" t="inlineStr"/>
-      <c r="Q85" s="1" t="inlineStr"/>
-      <c r="R85" s="1" t="inlineStr"/>
-      <c r="S85" s="1" t="inlineStr"/>
-      <c r="T85" s="1" t="inlineStr"/>
-      <c r="U85" s="1" t="inlineStr"/>
-      <c r="V85" s="1" t="inlineStr"/>
-      <c r="W85" s="1" t="inlineStr"/>
-      <c r="X85" s="1" t="inlineStr"/>
-      <c r="Y85" s="1" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr"/>
-      <c r="B86" s="1" t="inlineStr"/>
-      <c r="C86" s="1" t="inlineStr"/>
-      <c r="D86" s="1" t="inlineStr"/>
-      <c r="E86" s="1" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr"/>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Pittsburg .......000000010â€”1 3 1</t>
-        </is>
-      </c>
-      <c r="L86" s="1" t="inlineStr"/>
-      <c r="M86" s="1" t="inlineStr"/>
-      <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr"/>
-      <c r="P86" s="1" t="inlineStr"/>
-      <c r="Q86" s="1" t="inlineStr"/>
-      <c r="R86" s="1" t="inlineStr"/>
-      <c r="S86" s="1" t="inlineStr"/>
-      <c r="T86" s="1" t="inlineStr"/>
-      <c r="U86" s="1" t="inlineStr"/>
-      <c r="V86" s="1" t="inlineStr"/>
-      <c r="W86" s="1" t="inlineStr"/>
-      <c r="X86" s="1" t="inlineStr"/>
-      <c r="Y86" s="1" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="inlineStr"/>
-      <c r="B87" s="1" t="inlineStr"/>
-      <c r="C87" s="1" t="inlineStr"/>
-      <c r="D87" s="1" t="inlineStr"/>
-      <c r="E87" s="1" t="inlineStr"/>
-      <c r="F87" s="1" t="inlineStr"/>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L866: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Demaree, Marquard and</t>
-        </is>
-      </c>
-      <c r="L87" s="1" t="inlineStr"/>
-      <c r="M87" s="1" t="inlineStr"/>
-      <c r="N87" s="1" t="inlineStr"/>
-      <c r="O87" s="1" t="inlineStr"/>
-      <c r="P87" s="1" t="inlineStr"/>
-      <c r="Q87" s="1" t="inlineStr"/>
-      <c r="R87" s="1" t="inlineStr"/>
-      <c r="S87" s="1" t="inlineStr"/>
-      <c r="T87" s="1" t="inlineStr"/>
-      <c r="U87" s="1" t="inlineStr"/>
-      <c r="V87" s="1" t="inlineStr"/>
-      <c r="W87" s="1" t="inlineStr"/>
-      <c r="X87" s="1" t="inlineStr"/>
-      <c r="Y87" s="1" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr"/>
-      <c r="B88" s="1" t="inlineStr"/>
-      <c r="C88" s="1" t="inlineStr"/>
-      <c r="D88" s="1" t="inlineStr"/>
-      <c r="E88" s="1" t="inlineStr"/>
-      <c r="F88" s="1" t="inlineStr"/>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L870: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: At Cincinnatiâ€”</t>
-        </is>
-      </c>
-      <c r="L88" s="1" t="inlineStr"/>
-      <c r="M88" s="1" t="inlineStr"/>
-      <c r="N88" s="1" t="inlineStr"/>
-      <c r="O88" s="1" t="inlineStr"/>
-      <c r="P88" s="1" t="inlineStr"/>
-      <c r="Q88" s="1" t="inlineStr"/>
-      <c r="R88" s="1" t="inlineStr"/>
-      <c r="S88" s="1" t="inlineStr"/>
-      <c r="T88" s="1" t="inlineStr"/>
-      <c r="U88" s="1" t="inlineStr"/>
-      <c r="V88" s="1" t="inlineStr"/>
-      <c r="W88" s="1" t="inlineStr"/>
-      <c r="X88" s="1" t="inlineStr"/>
-      <c r="Y88" s="1" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr"/>
-      <c r="B89" s="1" t="inlineStr"/>
-      <c r="C89" s="1" t="inlineStr"/>
-      <c r="D89" s="1" t="inlineStr"/>
-      <c r="E89" s="1" t="inlineStr"/>
-      <c r="F89" s="1" t="inlineStr"/>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): 04020223x (letter/digit mix) :: Cincinnati......04020223xâ€”13 19 1</t>
-        </is>
-      </c>
-      <c r="L89" s="1" t="inlineStr"/>
-      <c r="M89" s="1" t="inlineStr"/>
-      <c r="N89" s="1" t="inlineStr"/>
-      <c r="O89" s="1" t="inlineStr"/>
-      <c r="P89" s="1" t="inlineStr"/>
-      <c r="Q89" s="1" t="inlineStr"/>
-      <c r="R89" s="1" t="inlineStr"/>
-      <c r="S89" s="1" t="inlineStr"/>
-      <c r="T89" s="1" t="inlineStr"/>
-      <c r="U89" s="1" t="inlineStr"/>
-      <c r="V89" s="1" t="inlineStr"/>
-      <c r="W89" s="1" t="inlineStr"/>
-      <c r="X89" s="1" t="inlineStr"/>
-      <c r="Y89" s="1" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="inlineStr"/>
-      <c r="B90" s="1" t="inlineStr"/>
-      <c r="C90" s="1" t="inlineStr"/>
-      <c r="D90" s="1" t="inlineStr"/>
-      <c r="E90" s="1" t="inlineStr"/>
-      <c r="F90" s="1" t="inlineStr"/>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr"/>
-      <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Boston..........120000001â€” 4 7 1</t>
-        </is>
-      </c>
-      <c r="L90" s="1" t="inlineStr"/>
-      <c r="M90" s="1" t="inlineStr"/>
-      <c r="N90" s="1" t="inlineStr"/>
-      <c r="O90" s="1" t="inlineStr"/>
-      <c r="P90" s="1" t="inlineStr"/>
-      <c r="Q90" s="1" t="inlineStr"/>
-      <c r="R90" s="1" t="inlineStr"/>
-      <c r="S90" s="1" t="inlineStr"/>
-      <c r="T90" s="1" t="inlineStr"/>
-      <c r="U90" s="1" t="inlineStr"/>
-      <c r="V90" s="1" t="inlineStr"/>
-      <c r="W90" s="1" t="inlineStr"/>
-      <c r="X90" s="1" t="inlineStr"/>
-      <c r="Y90" s="1" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="inlineStr"/>
-      <c r="B91" s="1" t="inlineStr"/>
-      <c r="C91" s="1" t="inlineStr"/>
-      <c r="D91" s="1" t="inlineStr"/>
-      <c r="E91" s="1" t="inlineStr"/>
-      <c r="F91" s="1" t="inlineStr"/>
-      <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
-      <c r="I91" s="1" t="inlineStr"/>
-      <c r="J91" s="1" t="inlineStr"/>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L876: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Batteriesâ€”Rudolph, Noyes</t>
-        </is>
-      </c>
-      <c r="L91" s="1" t="inlineStr"/>
-      <c r="M91" s="1" t="inlineStr"/>
-      <c r="N91" s="1" t="inlineStr"/>
-      <c r="O91" s="1" t="inlineStr"/>
-      <c r="P91" s="1" t="inlineStr"/>
-      <c r="Q91" s="1" t="inlineStr"/>
-      <c r="R91" s="1" t="inlineStr"/>
-      <c r="S91" s="1" t="inlineStr"/>
-      <c r="T91" s="1" t="inlineStr"/>
-      <c r="U91" s="1" t="inlineStr"/>
-      <c r="V91" s="1" t="inlineStr"/>
-      <c r="W91" s="1" t="inlineStr"/>
-      <c r="X91" s="1" t="inlineStr"/>
-      <c r="Y91" s="1" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="inlineStr"/>
-      <c r="B92" s="1" t="inlineStr"/>
-      <c r="C92" s="1" t="inlineStr"/>
-      <c r="D92" s="1" t="inlineStr"/>
-      <c r="E92" s="1" t="inlineStr"/>
-      <c r="F92" s="1" t="inlineStr"/>
-      <c r="G92" s="1" t="inlineStr"/>
-      <c r="H92" s="1" t="inlineStr"/>
-      <c r="I92" s="1" t="inlineStr"/>
-      <c r="J92" s="1" t="inlineStr"/>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>L894: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” , â€” the finest selected american leaf tobacco.</t>
-        </is>
-      </c>
-      <c r="L92" s="1" t="inlineStr"/>
-      <c r="M92" s="1" t="inlineStr"/>
-      <c r="N92" s="1" t="inlineStr"/>
-      <c r="O92" s="1" t="inlineStr"/>
-      <c r="P92" s="1" t="inlineStr"/>
-      <c r="Q92" s="1" t="inlineStr"/>
-      <c r="R92" s="1" t="inlineStr"/>
-      <c r="S92" s="1" t="inlineStr"/>
-      <c r="T92" s="1" t="inlineStr"/>
-      <c r="U92" s="1" t="inlineStr"/>
-      <c r="V92" s="1" t="inlineStr"/>
-      <c r="W92" s="1" t="inlineStr"/>
-      <c r="X92" s="1" t="inlineStr"/>
-      <c r="Y92" s="1" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr"/>
-      <c r="B93" s="1" t="inlineStr"/>
-      <c r="C93" s="1" t="inlineStr"/>
-      <c r="D93" s="1" t="inlineStr"/>
-      <c r="E93" s="1" t="inlineStr"/>
-      <c r="F93" s="1" t="inlineStr"/>
-      <c r="G93" s="1" t="inlineStr"/>
-      <c r="H93" s="1" t="inlineStr"/>
-      <c r="I93" s="1" t="inlineStr"/>
-      <c r="J93" s="1" t="inlineStr"/>
-      <c r="K93" s="1" t="inlineStr">
-        <is>
-          <t>L921: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Phone 46.</t>
-        </is>
-      </c>
-      <c r="L93" s="1" t="inlineStr"/>
-      <c r="M93" s="1" t="inlineStr"/>
-      <c r="N93" s="1" t="inlineStr"/>
-      <c r="O93" s="1" t="inlineStr"/>
-      <c r="P93" s="1" t="inlineStr"/>
-      <c r="Q93" s="1" t="inlineStr"/>
-      <c r="R93" s="1" t="inlineStr"/>
-      <c r="S93" s="1" t="inlineStr"/>
-      <c r="T93" s="1" t="inlineStr"/>
-      <c r="U93" s="1" t="inlineStr"/>
-      <c r="V93" s="1" t="inlineStr"/>
-      <c r="W93" s="1" t="inlineStr"/>
-      <c r="X93" s="1" t="inlineStr"/>
-      <c r="Y93" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
